--- a/artfynd/A 53262-2025 artfynd.xlsx
+++ b/artfynd/A 53262-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1422,6 +1422,9625 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129709811</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>618429</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6974460</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129709813</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>618387</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6974489</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129709780</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>185</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>618429</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6974460</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129709783</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>618335</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6974445</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129698674</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91551</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>618306</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6974462</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129698621</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>618317</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6974462</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129703570</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>618374</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6974569</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129709792</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80208</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>618361</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6974581</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129709781</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>618592</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6974467</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129698604</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80084</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>618306</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6974462</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129699517</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>618397</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6974439</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129699006</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80208</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>618388</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6974505</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129709806</v>
+      </c>
+      <c r="B20" t="n">
+        <v>105834</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>618257</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6974614</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129709801</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>618563</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6974457</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>110 stycken</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129700331</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>618459</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6974445</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129709808</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>618368</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6974577</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129703715</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91601</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>618370</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6974548</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129699154</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>618371</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6974482</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129700673</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>618551</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6974411</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Sav/kåda syns från ett antal rader högt upp</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129705121</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>618113</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6974574</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129704326</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>618265</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6974595</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129699831</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>618439</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6974411</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129703585</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80209</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>618374</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6974569</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129705042</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>658</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>618126</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6974589</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129705214</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>618074</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6974557</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129709797</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>618255</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6974610</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>70 exemplar ca</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129709788</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91608</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>618455</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6974515</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129698910</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>618360</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6974490</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Svårt att säga exakt antal då det var lite översnöat</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129704389</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>618258</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6974606</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129709803</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>618554</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6974421</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>14 exemplar ca</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129704306</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78833</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>618272</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6974601</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129701808</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80180</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>618645</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6974380</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129701823</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>618649</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6974391</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129700579</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>618530</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6974383</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129700722</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>618567</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6974393</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129704245</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>618265</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6974571</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129701961</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>618622</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6974425</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129700093</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80180</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>618480</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6974430</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129700433</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78832</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>618512</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6974407</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129702152</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>618609</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6974445</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129701912</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>618633</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6974410</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129709802</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>618567</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6974470</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>100stycken ca</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129700894</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>618592</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6974393</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129709804</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>618371</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6974493</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>100 stycken ca</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129704213</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78832</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>618281</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6974552</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129698501</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>618299</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6974415</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129709790</v>
+      </c>
+      <c r="B54" t="n">
+        <v>97639</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>618431</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6974524</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129700660</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>618570</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6974419</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129709795</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>618177</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6974631</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>33 stycken ca</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129703746</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>618374</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6974569</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129701951</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>618605</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6974424</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhck av tretåig hackspett på tall</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129702559</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>618561</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6974470</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129709786</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>618556</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6974460</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>2 stycken, födosöker. Övriga läten</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129701964</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>618599</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6974439</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129709791</v>
+      </c>
+      <c r="B62" t="n">
+        <v>97639</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>618571</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6974415</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129698818</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>618341</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6974479</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129709787</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>618429</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6974460</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Övriga läten</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129700395</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>618472</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6974404</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Kan finnas mer under löven</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129709799</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>618358</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6974576</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>100 stycken ca</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129709810</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>618631</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6974375</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129709809</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>618431</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6974524</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129704771</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91601</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>618289</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6974621</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129701187</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>618641</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6974337</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129709782</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>618425</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6974448</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129699772</v>
+      </c>
+      <c r="B72" t="n">
+        <v>97639</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>618405</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6974427</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129701841</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>658</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>618649</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6974391</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129709800</v>
+      </c>
+      <c r="B74" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>618497</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6974486</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>11 stycken ca</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129702470</v>
+      </c>
+      <c r="B75" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>618556</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6974479</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129709794</v>
+      </c>
+      <c r="B76" t="n">
+        <v>80180</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>618395</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6974510</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129704757</v>
+      </c>
+      <c r="B77" t="n">
+        <v>91760</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>618292</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6974613</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129702960</v>
+      </c>
+      <c r="B78" t="n">
+        <v>78832</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>618489</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6974558</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129699521</v>
+      </c>
+      <c r="B79" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>658</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>618397</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6974439</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129700014</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>618472</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6974404</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129709807</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91607</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>618463</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6974461</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129709798</v>
+      </c>
+      <c r="B82" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>618348</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6974608</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>36 stycken ca</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129699933</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>618429</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6974385</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129699496</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>618397</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6974439</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>129703426</v>
+      </c>
+      <c r="B85" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>658</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>618409</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6974571</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129709805</v>
+      </c>
+      <c r="B86" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>618377</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6974494</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>40 exemplar</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>129709796</v>
+      </c>
+      <c r="B87" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>618180</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6974638</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>9 stycken</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>129703590</v>
+      </c>
+      <c r="B88" t="n">
+        <v>80180</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>618374</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6974569</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>129704982</v>
+      </c>
+      <c r="B89" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>618170</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6974612</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>129700937</v>
+      </c>
+      <c r="B90" t="n">
+        <v>90619</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>618593</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6974355</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>129702218</v>
+      </c>
+      <c r="B91" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>618623</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6974450</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>129700358</v>
+      </c>
+      <c r="B92" t="n">
+        <v>97639</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>618459</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6974445</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129699107</v>
+      </c>
+      <c r="B93" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>618371</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6974482</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129709793</v>
+      </c>
+      <c r="B94" t="n">
+        <v>80208</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>618444</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6974454</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>129703072</v>
+      </c>
+      <c r="B95" t="n">
+        <v>80208</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>618475</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6974567</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>129698786</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>618352</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6974455</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>129700040</v>
+      </c>
+      <c r="B97" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>618488</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6974408</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Många äldre ringhack, men en färsk rad</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>129700503</v>
+      </c>
+      <c r="B98" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>618531</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6974409</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>129703875</v>
+      </c>
+      <c r="B99" t="n">
+        <v>88986</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>510</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>618370</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6974548</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>129705055</v>
+      </c>
+      <c r="B100" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>618126</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6974604</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>129701836</v>
+      </c>
+      <c r="B101" t="n">
+        <v>92040</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>618649</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6974391</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>129699630</v>
+      </c>
+      <c r="B102" t="n">
+        <v>78833</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>618397</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6974439</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>129701956</v>
+      </c>
+      <c r="B103" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>618623</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6974433</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Tyvärr dålig video, men innan inspelningen såg jag den väl i kikaren.</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53262-2025 artfynd.xlsx
+++ b/artfynd/A 53262-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY103"/>
+  <dimension ref="A1:AY104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129709811</v>
+        <v>129709780</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,21 +1436,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129709813</v>
+        <v>129709811</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618387</v>
+        <v>618429</v>
       </c>
       <c r="R9" t="n">
-        <v>6974489</v>
+        <v>6974460</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129709780</v>
+        <v>129709813</v>
       </c>
       <c r="B10" t="n">
-        <v>79107</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,21 +1630,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618429</v>
+        <v>618387</v>
       </c>
       <c r="R10" t="n">
-        <v>6974460</v>
+        <v>6974489</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129709783</v>
+        <v>129698621</v>
       </c>
       <c r="B11" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,16 +1745,21 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618335</v>
+        <v>618317</v>
       </c>
       <c r="R11" t="n">
-        <v>6974445</v>
+        <v>6974462</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1796,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre spår, ringhack av tretåig hackspett</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,32 +1823,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129698674</v>
+        <v>129709783</v>
       </c>
       <c r="B12" t="n">
-        <v>91551</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1853,10 +1858,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618306</v>
+        <v>618335</v>
       </c>
       <c r="R12" t="n">
-        <v>6974462</v>
+        <v>6974445</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,6 +1894,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,50 +1925,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129698621</v>
+        <v>129703570</v>
       </c>
       <c r="B13" t="n">
-        <v>57735</v>
+        <v>80141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618317</v>
+        <v>618374</v>
       </c>
       <c r="R13" t="n">
-        <v>6974462</v>
+        <v>6974569</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1991,11 +1996,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129703570</v>
+        <v>129698674</v>
       </c>
       <c r="B14" t="n">
-        <v>80140</v>
+        <v>91552</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,21 +2033,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618374</v>
+        <v>618306</v>
       </c>
       <c r="R14" t="n">
-        <v>6974569</v>
+        <v>6974462</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129709792</v>
+        <v>129698604</v>
       </c>
       <c r="B15" t="n">
-        <v>80208</v>
+        <v>80085</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,21 +2130,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618361</v>
+        <v>618306</v>
       </c>
       <c r="R15" t="n">
-        <v>6974581</v>
+        <v>6974462</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,32 +2216,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129709781</v>
+        <v>129709792</v>
       </c>
       <c r="B16" t="n">
-        <v>57735</v>
+        <v>80209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618592</v>
+        <v>618361</v>
       </c>
       <c r="R16" t="n">
-        <v>6974467</v>
+        <v>6974581</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2287,11 +2287,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2318,32 +2313,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129698604</v>
+        <v>129709781</v>
       </c>
       <c r="B17" t="n">
-        <v>80084</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2353,10 +2348,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618306</v>
+        <v>618592</v>
       </c>
       <c r="R17" t="n">
-        <v>6974462</v>
+        <v>6974467</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,6 +2384,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2415,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129699517</v>
+        <v>129709808</v>
       </c>
       <c r="B18" t="n">
-        <v>91587</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,21 +2426,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>618397</v>
+        <v>618368</v>
       </c>
       <c r="R18" t="n">
-        <v>6974439</v>
+        <v>6974577</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2515,7 +2515,7 @@
         <v>129699006</v>
       </c>
       <c r="B19" t="n">
-        <v>80208</v>
+        <v>80209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,32 +2609,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129709806</v>
+        <v>129703715</v>
       </c>
       <c r="B20" t="n">
-        <v>105834</v>
+        <v>91602</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>618257</v>
+        <v>618370</v>
       </c>
       <c r="R20" t="n">
-        <v>6974614</v>
+        <v>6974548</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2706,32 +2706,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129709801</v>
+        <v>129699517</v>
       </c>
       <c r="B21" t="n">
-        <v>98768</v>
+        <v>91588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>618563</v>
+        <v>618397</v>
       </c>
       <c r="R21" t="n">
-        <v>6974457</v>
+        <v>6974439</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2777,11 +2777,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>110 stycken</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2808,10 +2803,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129700331</v>
+        <v>129709801</v>
       </c>
       <c r="B22" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,21 +2831,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>618459</v>
+        <v>618563</v>
       </c>
       <c r="R22" t="n">
-        <v>6974445</v>
+        <v>6974457</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2883,6 +2874,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>110 stycken</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2909,45 +2905,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129709808</v>
+        <v>129700331</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>618368</v>
+        <v>618459</v>
       </c>
       <c r="R23" t="n">
-        <v>6974577</v>
+        <v>6974445</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3006,32 +3006,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129703715</v>
+        <v>129709806</v>
       </c>
       <c r="B24" t="n">
-        <v>91601</v>
+        <v>105835</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>618370</v>
+        <v>618257</v>
       </c>
       <c r="R24" t="n">
-        <v>6974548</v>
+        <v>6974614</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129699154</v>
+        <v>129700673</v>
       </c>
       <c r="B25" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>618371</v>
+        <v>618551</v>
       </c>
       <c r="R25" t="n">
-        <v>6974482</v>
+        <v>6974411</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall. Sav/kåda syns från ett antal rader högt upp</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3210,10 +3210,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129700673</v>
+        <v>129699154</v>
       </c>
       <c r="B26" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>618551</v>
+        <v>618371</v>
       </c>
       <c r="R26" t="n">
-        <v>6974411</v>
+        <v>6974482</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Sav/kåda syns från ett antal rader högt upp</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3320,7 +3320,7 @@
         <v>129705121</v>
       </c>
       <c r="B27" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>129704326</v>
       </c>
       <c r="B28" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,49 +3511,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129699831</v>
+        <v>129703585</v>
       </c>
       <c r="B29" t="n">
-        <v>98768</v>
+        <v>80210</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>618439</v>
+        <v>618374</v>
       </c>
       <c r="R29" t="n">
-        <v>6974411</v>
+        <v>6974569</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3612,45 +3608,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129703585</v>
+        <v>129705214</v>
       </c>
       <c r="B30" t="n">
-        <v>80209</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>618374</v>
+        <v>618074</v>
       </c>
       <c r="R30" t="n">
-        <v>6974569</v>
+        <v>6974557</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3683,6 +3684,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3709,45 +3715,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129705042</v>
+        <v>129699831</v>
       </c>
       <c r="B31" t="n">
-        <v>91885</v>
+        <v>98769</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>618126</v>
+        <v>618439</v>
       </c>
       <c r="R31" t="n">
-        <v>6974589</v>
+        <v>6974411</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3806,10 +3816,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129705214</v>
+        <v>129705042</v>
       </c>
       <c r="B32" t="n">
-        <v>57735</v>
+        <v>91886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3817,39 +3827,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>618074</v>
+        <v>618126</v>
       </c>
       <c r="R32" t="n">
-        <v>6974557</v>
+        <v>6974589</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3882,11 +3887,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3916,7 +3916,7 @@
         <v>129709797</v>
       </c>
       <c r="B33" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4015,45 +4015,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129709788</v>
+        <v>129698910</v>
       </c>
       <c r="B34" t="n">
-        <v>91608</v>
+        <v>98769</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>618455</v>
+        <v>618360</v>
       </c>
       <c r="R34" t="n">
-        <v>6974515</v>
+        <v>6974490</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4086,6 +4090,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Svårt att säga exakt antal då det var lite översnöat</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4112,10 +4121,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129698910</v>
+        <v>129709803</v>
       </c>
       <c r="B35" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4140,21 +4149,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>618360</v>
+        <v>618554</v>
       </c>
       <c r="R35" t="n">
-        <v>6974490</v>
+        <v>6974421</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4191,7 +4196,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Svårt att säga exakt antal då det var lite översnöat</t>
+          <t>14 exemplar ca</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4218,49 +4223,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129704389</v>
+        <v>129704306</v>
       </c>
       <c r="B36" t="n">
-        <v>98768</v>
+        <v>78834</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>618258</v>
+        <v>618272</v>
       </c>
       <c r="R36" t="n">
-        <v>6974606</v>
+        <v>6974601</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4319,10 +4320,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129709803</v>
+        <v>129704389</v>
       </c>
       <c r="B37" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4347,17 +4348,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>618554</v>
+        <v>618258</v>
       </c>
       <c r="R37" t="n">
-        <v>6974421</v>
+        <v>6974606</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4390,11 +4395,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>14 exemplar ca</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4421,10 +4421,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129704306</v>
+        <v>129709788</v>
       </c>
       <c r="B38" t="n">
-        <v>78833</v>
+        <v>91609</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4432,21 +4432,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>618272</v>
+        <v>618455</v>
       </c>
       <c r="R38" t="n">
-        <v>6974601</v>
+        <v>6974515</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4518,10 +4518,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129701808</v>
+        <v>129701823</v>
       </c>
       <c r="B39" t="n">
-        <v>80180</v>
+        <v>91588</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4529,21 +4529,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4553,10 +4553,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>618645</v>
+        <v>618649</v>
       </c>
       <c r="R39" t="n">
-        <v>6974380</v>
+        <v>6974391</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129701823</v>
+        <v>129700579</v>
       </c>
       <c r="B40" t="n">
-        <v>91587</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4626,34 +4626,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>618649</v>
+        <v>618530</v>
       </c>
       <c r="R40" t="n">
-        <v>6974391</v>
+        <v>6974383</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4686,6 +4691,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4712,10 +4722,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129700579</v>
+        <v>129700722</v>
       </c>
       <c r="B41" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4752,10 +4762,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>618530</v>
+        <v>618567</v>
       </c>
       <c r="R41" t="n">
-        <v>6974383</v>
+        <v>6974393</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4819,50 +4829,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129700722</v>
+        <v>129701961</v>
       </c>
       <c r="B42" t="n">
-        <v>57735</v>
+        <v>80141</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>618567</v>
+        <v>618622</v>
       </c>
       <c r="R42" t="n">
-        <v>6974393</v>
+        <v>6974425</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4895,11 +4900,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4929,7 +4929,7 @@
         <v>129704245</v>
       </c>
       <c r="B43" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5027,32 +5027,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129701961</v>
+        <v>129701808</v>
       </c>
       <c r="B44" t="n">
-        <v>80140</v>
+        <v>80181</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>618622</v>
+        <v>618645</v>
       </c>
       <c r="R44" t="n">
-        <v>6974425</v>
+        <v>6974380</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5127,7 +5127,7 @@
         <v>129700093</v>
       </c>
       <c r="B45" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>129700433</v>
       </c>
       <c r="B46" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5318,32 +5318,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129702152</v>
+        <v>129709804</v>
       </c>
       <c r="B47" t="n">
-        <v>91587</v>
+        <v>98769</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>618609</v>
+        <v>618371</v>
       </c>
       <c r="R47" t="n">
-        <v>6974445</v>
+        <v>6974493</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5389,6 +5389,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>100 stycken ca</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5415,10 +5420,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129701912</v>
+        <v>129702152</v>
       </c>
       <c r="B48" t="n">
-        <v>57732</v>
+        <v>91588</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5426,39 +5431,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>618633</v>
+        <v>618609</v>
       </c>
       <c r="R48" t="n">
-        <v>6974410</v>
+        <v>6974445</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5517,45 +5517,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129709802</v>
+        <v>129701912</v>
       </c>
       <c r="B49" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>618567</v>
+        <v>618633</v>
       </c>
       <c r="R49" t="n">
-        <v>6974470</v>
+        <v>6974410</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5588,11 +5593,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>100stycken ca</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5622,7 +5622,7 @@
         <v>129700894</v>
       </c>
       <c r="B50" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5720,10 +5720,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129709804</v>
+        <v>129709802</v>
       </c>
       <c r="B51" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>618371</v>
+        <v>618567</v>
       </c>
       <c r="R51" t="n">
-        <v>6974493</v>
+        <v>6974470</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>100 stycken ca</t>
+          <t>100stycken ca</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5825,7 +5825,7 @@
         <v>129704213</v>
       </c>
       <c r="B52" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5919,10 +5919,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129698501</v>
+        <v>129700660</v>
       </c>
       <c r="B53" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5959,10 +5959,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>618299</v>
+        <v>618570</v>
       </c>
       <c r="R53" t="n">
-        <v>6974415</v>
+        <v>6974419</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6026,32 +6026,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129709790</v>
+        <v>129709795</v>
       </c>
       <c r="B54" t="n">
-        <v>97639</v>
+        <v>98769</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>618431</v>
+        <v>618177</v>
       </c>
       <c r="R54" t="n">
-        <v>6974524</v>
+        <v>6974631</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6097,6 +6097,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>33 stycken ca</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6123,50 +6128,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129700660</v>
+        <v>129709790</v>
       </c>
       <c r="B55" t="n">
-        <v>57735</v>
+        <v>97640</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>618570</v>
+        <v>618431</v>
       </c>
       <c r="R55" t="n">
-        <v>6974419</v>
+        <v>6974524</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6199,11 +6199,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6230,45 +6225,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129709795</v>
+        <v>129698501</v>
       </c>
       <c r="B56" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>618177</v>
+        <v>618299</v>
       </c>
       <c r="R56" t="n">
-        <v>6974631</v>
+        <v>6974415</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>33 stycken ca</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6335,7 +6335,7 @@
         <v>129703746</v>
       </c>
       <c r="B57" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6429,10 +6429,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129701951</v>
+        <v>129702559</v>
       </c>
       <c r="B58" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>618605</v>
+        <v>618561</v>
       </c>
       <c r="R58" t="n">
-        <v>6974424</v>
+        <v>6974470</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhck av tretåig hackspett på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6536,10 +6536,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129702559</v>
+        <v>129701951</v>
       </c>
       <c r="B59" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>618561</v>
+        <v>618605</v>
       </c>
       <c r="R59" t="n">
-        <v>6974470</v>
+        <v>6974424</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhck av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6646,7 +6646,7 @@
         <v>129709786</v>
       </c>
       <c r="B60" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>129701964</v>
       </c>
       <c r="B61" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>129709791</v>
       </c>
       <c r="B62" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>129698818</v>
       </c>
       <c r="B63" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7044,10 +7044,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129709787</v>
+        <v>129704771</v>
       </c>
       <c r="B64" t="n">
-        <v>57895</v>
+        <v>91602</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7055,21 +7055,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7079,10 +7079,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>618429</v>
+        <v>618289</v>
       </c>
       <c r="R64" t="n">
-        <v>6974460</v>
+        <v>6974621</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Övriga läten</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7146,49 +7146,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129700395</v>
+        <v>129709810</v>
       </c>
       <c r="B65" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>618472</v>
+        <v>618631</v>
       </c>
       <c r="R65" t="n">
-        <v>6974404</v>
+        <v>6974375</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7221,11 +7217,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Kan finnas mer under löven</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7252,32 +7243,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129709799</v>
+        <v>129709809</v>
       </c>
       <c r="B66" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7287,10 +7278,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>618358</v>
+        <v>618431</v>
       </c>
       <c r="R66" t="n">
-        <v>6974576</v>
+        <v>6974524</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7323,11 +7314,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>100 stycken ca</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7354,10 +7340,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129709810</v>
+        <v>129709787</v>
       </c>
       <c r="B67" t="n">
-        <v>79075</v>
+        <v>57896</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7365,21 +7351,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7389,10 +7375,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>618631</v>
+        <v>618429</v>
       </c>
       <c r="R67" t="n">
-        <v>6974375</v>
+        <v>6974460</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7425,6 +7411,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Övriga läten</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7451,45 +7442,49 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129709809</v>
+        <v>129700395</v>
       </c>
       <c r="B68" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>618431</v>
+        <v>618472</v>
       </c>
       <c r="R68" t="n">
-        <v>6974524</v>
+        <v>6974404</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7522,6 +7517,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Kan finnas mer under löven</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7548,32 +7548,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129704771</v>
+        <v>129709799</v>
       </c>
       <c r="B69" t="n">
-        <v>91601</v>
+        <v>98769</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7583,10 +7583,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>618289</v>
+        <v>618358</v>
       </c>
       <c r="R69" t="n">
-        <v>6974621</v>
+        <v>6974576</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>100 stycken ca</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7653,7 +7653,7 @@
         <v>129701187</v>
       </c>
       <c r="B70" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>129709782</v>
       </c>
       <c r="B71" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>129699772</v>
       </c>
       <c r="B72" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>129701841</v>
       </c>
       <c r="B73" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8043,10 +8043,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129709800</v>
+        <v>129702470</v>
       </c>
       <c r="B74" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8071,17 +8071,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>618497</v>
+        <v>618556</v>
       </c>
       <c r="R74" t="n">
-        <v>6974486</v>
+        <v>6974479</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8114,11 +8118,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>11 stycken ca</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8145,10 +8144,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129702470</v>
+        <v>129709800</v>
       </c>
       <c r="B75" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8173,21 +8172,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>618556</v>
+        <v>618497</v>
       </c>
       <c r="R75" t="n">
-        <v>6974479</v>
+        <v>6974486</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8220,6 +8215,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>11 stycken ca</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8246,32 +8246,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129709794</v>
+        <v>129704757</v>
       </c>
       <c r="B76" t="n">
-        <v>80180</v>
+        <v>91761</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>618395</v>
+        <v>618292</v>
       </c>
       <c r="R76" t="n">
-        <v>6974510</v>
+        <v>6974613</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8343,32 +8343,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129704757</v>
+        <v>129709794</v>
       </c>
       <c r="B77" t="n">
-        <v>91760</v>
+        <v>80181</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8378,10 +8378,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>618292</v>
+        <v>618395</v>
       </c>
       <c r="R77" t="n">
-        <v>6974613</v>
+        <v>6974510</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8443,7 +8443,7 @@
         <v>129702960</v>
       </c>
       <c r="B78" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>129699521</v>
       </c>
       <c r="B79" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8634,10 +8634,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129700014</v>
+        <v>129709807</v>
       </c>
       <c r="B80" t="n">
-        <v>57735</v>
+        <v>91608</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8645,39 +8645,30 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>618472</v>
+        <v>618463</v>
       </c>
       <c r="R80" t="n">
-        <v>6974404</v>
+        <v>6974461</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8710,11 +8701,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8741,10 +8727,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129709807</v>
+        <v>129700014</v>
       </c>
       <c r="B81" t="n">
-        <v>91607</v>
+        <v>57736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8752,30 +8738,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>618463</v>
+        <v>618472</v>
       </c>
       <c r="R81" t="n">
-        <v>6974461</v>
+        <v>6974404</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8808,6 +8803,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8837,7 +8837,7 @@
         <v>129709798</v>
       </c>
       <c r="B82" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8936,10 +8936,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129699933</v>
+        <v>129703426</v>
       </c>
       <c r="B83" t="n">
-        <v>57735</v>
+        <v>91886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8947,39 +8947,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>618429</v>
+        <v>618409</v>
       </c>
       <c r="R83" t="n">
-        <v>6974385</v>
+        <v>6974571</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9012,11 +9007,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9043,10 +9033,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129699496</v>
+        <v>129699933</v>
       </c>
       <c r="B84" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9074,7 +9064,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9083,10 +9073,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>618397</v>
+        <v>618429</v>
       </c>
       <c r="R84" t="n">
-        <v>6974439</v>
+        <v>6974385</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9150,10 +9140,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129703426</v>
+        <v>129699496</v>
       </c>
       <c r="B85" t="n">
-        <v>91885</v>
+        <v>57736</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9161,34 +9151,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>618409</v>
+        <v>618397</v>
       </c>
       <c r="R85" t="n">
-        <v>6974571</v>
+        <v>6974439</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9221,6 +9216,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9250,7 +9250,7 @@
         <v>129709805</v>
       </c>
       <c r="B86" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>129709796</v>
       </c>
       <c r="B87" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9451,10 +9451,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129703590</v>
+        <v>129704982</v>
       </c>
       <c r="B88" t="n">
-        <v>80180</v>
+        <v>91588</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9462,21 +9462,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9486,10 +9486,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>618374</v>
+        <v>618170</v>
       </c>
       <c r="R88" t="n">
-        <v>6974569</v>
+        <v>6974612</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9548,10 +9548,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129704982</v>
+        <v>129702218</v>
       </c>
       <c r="B89" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9583,10 +9583,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>618170</v>
+        <v>618623</v>
       </c>
       <c r="R89" t="n">
-        <v>6974612</v>
+        <v>6974450</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9648,7 +9648,7 @@
         <v>129700937</v>
       </c>
       <c r="B90" t="n">
-        <v>90619</v>
+        <v>90620</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9742,10 +9742,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129702218</v>
+        <v>129703590</v>
       </c>
       <c r="B91" t="n">
-        <v>91587</v>
+        <v>80181</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9753,21 +9753,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>618623</v>
+        <v>618374</v>
       </c>
       <c r="R91" t="n">
-        <v>6974450</v>
+        <v>6974569</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9839,32 +9839,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129700358</v>
+        <v>129698786</v>
       </c>
       <c r="B92" t="n">
-        <v>97639</v>
+        <v>79076</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9874,10 +9874,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>618459</v>
+        <v>618352</v>
       </c>
       <c r="R92" t="n">
-        <v>6974445</v>
+        <v>6974455</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9939,7 +9939,7 @@
         <v>129699107</v>
       </c>
       <c r="B93" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>129709793</v>
       </c>
       <c r="B94" t="n">
-        <v>80208</v>
+        <v>80209</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>129703072</v>
       </c>
       <c r="B95" t="n">
-        <v>80208</v>
+        <v>80209</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10231,32 +10231,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129698786</v>
+        <v>129700358</v>
       </c>
       <c r="B96" t="n">
-        <v>79075</v>
+        <v>97640</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10266,10 +10266,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>618352</v>
+        <v>618459</v>
       </c>
       <c r="R96" t="n">
-        <v>6974455</v>
+        <v>6974445</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10328,10 +10328,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129700040</v>
+        <v>129705055</v>
       </c>
       <c r="B97" t="n">
-        <v>57735</v>
+        <v>91588</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10339,39 +10339,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>618488</v>
+        <v>618126</v>
       </c>
       <c r="R97" t="n">
-        <v>6974408</v>
+        <v>6974604</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10404,11 +10399,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Många äldre ringhack, men en färsk rad</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10435,50 +10425,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129700503</v>
+        <v>129701836</v>
       </c>
       <c r="B98" t="n">
-        <v>57735</v>
+        <v>92041</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>618531</v>
+        <v>618649</v>
       </c>
       <c r="R98" t="n">
-        <v>6974409</v>
+        <v>6974391</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10511,11 +10496,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10545,7 +10525,7 @@
         <v>129703875</v>
       </c>
       <c r="B99" t="n">
-        <v>88986</v>
+        <v>88987</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10639,10 +10619,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129705055</v>
+        <v>129700040</v>
       </c>
       <c r="B100" t="n">
-        <v>91587</v>
+        <v>57736</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10650,34 +10630,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>618126</v>
+        <v>618488</v>
       </c>
       <c r="R100" t="n">
-        <v>6974604</v>
+        <v>6974408</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10710,6 +10695,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Många äldre ringhack, men en färsk rad</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10736,45 +10726,50 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129701836</v>
+        <v>129700503</v>
       </c>
       <c r="B101" t="n">
-        <v>92040</v>
+        <v>57736</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>618649</v>
+        <v>618531</v>
       </c>
       <c r="R101" t="n">
-        <v>6974391</v>
+        <v>6974409</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10807,6 +10802,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10836,7 +10836,7 @@
         <v>129699630</v>
       </c>
       <c r="B102" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>129701956</v>
       </c>
       <c r="B103" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11041,6 +11041,112 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>129701109</v>
+      </c>
+      <c r="B104" t="n">
+        <v>91761</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Asketjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>618601</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6974365</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Artbestämd genom mikroskopering.</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53262-2025 artfynd.xlsx
+++ b/artfynd/A 53262-2025 artfynd.xlsx
@@ -7946,10 +7946,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129701841</v>
+        <v>129709794</v>
       </c>
       <c r="B73" t="n">
-        <v>91886</v>
+        <v>80181</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7957,21 +7957,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>618649</v>
+        <v>618395</v>
       </c>
       <c r="R73" t="n">
-        <v>6974391</v>
+        <v>6974510</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8043,49 +8043,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129702470</v>
+        <v>129701841</v>
       </c>
       <c r="B74" t="n">
-        <v>98769</v>
+        <v>91886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>618556</v>
+        <v>618649</v>
       </c>
       <c r="R74" t="n">
-        <v>6974479</v>
+        <v>6974391</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8144,10 +8140,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129709800</v>
+        <v>129704757</v>
       </c>
       <c r="B75" t="n">
-        <v>98769</v>
+        <v>91761</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8155,21 +8151,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8179,10 +8175,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>618497</v>
+        <v>618292</v>
       </c>
       <c r="R75" t="n">
-        <v>6974486</v>
+        <v>6974613</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8215,11 +8211,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>11 stycken ca</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8246,10 +8237,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129704757</v>
+        <v>129702470</v>
       </c>
       <c r="B76" t="n">
-        <v>91761</v>
+        <v>98769</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8257,34 +8248,38 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>618292</v>
+        <v>618556</v>
       </c>
       <c r="R76" t="n">
-        <v>6974613</v>
+        <v>6974479</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8343,32 +8338,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129709794</v>
+        <v>129709800</v>
       </c>
       <c r="B77" t="n">
-        <v>80181</v>
+        <v>98769</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8378,10 +8373,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>618395</v>
+        <v>618497</v>
       </c>
       <c r="R77" t="n">
-        <v>6974510</v>
+        <v>6974486</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8414,6 +8409,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>11 stycken ca</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8440,10 +8440,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129702960</v>
+        <v>129709807</v>
       </c>
       <c r="B78" t="n">
-        <v>78833</v>
+        <v>91608</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8451,23 +8451,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8475,10 +8471,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>618489</v>
+        <v>618463</v>
       </c>
       <c r="R78" t="n">
-        <v>6974558</v>
+        <v>6974461</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8537,10 +8533,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129699521</v>
+        <v>129700014</v>
       </c>
       <c r="B79" t="n">
-        <v>91886</v>
+        <v>57736</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8548,34 +8544,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>618397</v>
+        <v>618472</v>
       </c>
       <c r="R79" t="n">
-        <v>6974439</v>
+        <v>6974404</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8608,6 +8609,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8634,10 +8640,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129709807</v>
+        <v>129699521</v>
       </c>
       <c r="B80" t="n">
-        <v>91608</v>
+        <v>91886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8645,19 +8651,23 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -8665,10 +8675,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>618463</v>
+        <v>618397</v>
       </c>
       <c r="R80" t="n">
-        <v>6974461</v>
+        <v>6974439</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8727,50 +8737,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129700014</v>
+        <v>129709798</v>
       </c>
       <c r="B81" t="n">
-        <v>57736</v>
+        <v>98769</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>618472</v>
+        <v>618348</v>
       </c>
       <c r="R81" t="n">
-        <v>6974404</v>
+        <v>6974608</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8807,7 +8812,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>36 stycken ca</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8834,32 +8839,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129709798</v>
+        <v>129702960</v>
       </c>
       <c r="B82" t="n">
-        <v>98769</v>
+        <v>78833</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8869,10 +8874,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>618348</v>
+        <v>618489</v>
       </c>
       <c r="R82" t="n">
-        <v>6974608</v>
+        <v>6974558</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8905,11 +8910,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>36 stycken ca</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8936,10 +8936,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129703426</v>
+        <v>129699933</v>
       </c>
       <c r="B83" t="n">
-        <v>91886</v>
+        <v>57736</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8947,34 +8947,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>618409</v>
+        <v>618429</v>
       </c>
       <c r="R83" t="n">
-        <v>6974571</v>
+        <v>6974385</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9007,6 +9012,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9033,7 +9043,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129699933</v>
+        <v>129699496</v>
       </c>
       <c r="B84" t="n">
         <v>57736</v>
@@ -9064,7 +9074,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9073,10 +9083,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>618429</v>
+        <v>618397</v>
       </c>
       <c r="R84" t="n">
-        <v>6974385</v>
+        <v>6974439</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9140,10 +9150,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129699496</v>
+        <v>129703426</v>
       </c>
       <c r="B85" t="n">
-        <v>57736</v>
+        <v>91886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9151,39 +9161,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>618397</v>
+        <v>618409</v>
       </c>
       <c r="R85" t="n">
-        <v>6974439</v>
+        <v>6974571</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9216,11 +9221,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9349,32 +9349,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129709796</v>
+        <v>129704982</v>
       </c>
       <c r="B87" t="n">
-        <v>98769</v>
+        <v>91588</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9384,10 +9384,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>618180</v>
+        <v>618170</v>
       </c>
       <c r="R87" t="n">
-        <v>6974638</v>
+        <v>6974612</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9420,11 +9420,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>9 stycken</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9451,7 +9446,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129704982</v>
+        <v>129702218</v>
       </c>
       <c r="B88" t="n">
         <v>91588</v>
@@ -9486,10 +9481,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>618170</v>
+        <v>618623</v>
       </c>
       <c r="R88" t="n">
-        <v>6974612</v>
+        <v>6974450</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9548,10 +9543,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129702218</v>
+        <v>129700937</v>
       </c>
       <c r="B89" t="n">
-        <v>91588</v>
+        <v>90620</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9559,21 +9554,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>1962</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9583,10 +9578,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>618623</v>
+        <v>618593</v>
       </c>
       <c r="R89" t="n">
-        <v>6974450</v>
+        <v>6974355</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9645,10 +9640,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129700937</v>
+        <v>129703590</v>
       </c>
       <c r="B90" t="n">
-        <v>90620</v>
+        <v>80181</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9656,21 +9651,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1962</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9680,10 +9675,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>618593</v>
+        <v>618374</v>
       </c>
       <c r="R90" t="n">
-        <v>6974355</v>
+        <v>6974569</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9742,32 +9737,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129703590</v>
+        <v>129709796</v>
       </c>
       <c r="B91" t="n">
-        <v>80181</v>
+        <v>98769</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9777,10 +9772,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>618374</v>
+        <v>618180</v>
       </c>
       <c r="R91" t="n">
-        <v>6974569</v>
+        <v>6974638</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9813,6 +9808,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>9 stycken</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9936,49 +9936,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129699107</v>
+        <v>129700358</v>
       </c>
       <c r="B93" t="n">
-        <v>98769</v>
+        <v>97640</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>618371</v>
+        <v>618459</v>
       </c>
       <c r="R93" t="n">
-        <v>6974482</v>
+        <v>6974445</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10231,45 +10227,49 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129700358</v>
+        <v>129699107</v>
       </c>
       <c r="B96" t="n">
-        <v>97640</v>
+        <v>98769</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>618459</v>
+        <v>618371</v>
       </c>
       <c r="R96" t="n">
-        <v>6974445</v>
+        <v>6974482</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>

--- a/artfynd/A 53262-2025 artfynd.xlsx
+++ b/artfynd/A 53262-2025 artfynd.xlsx
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129709780</v>
+        <v>129709811</v>
       </c>
       <c r="B8" t="n">
-        <v>79108</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,21 +1436,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129709811</v>
+        <v>129709813</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618429</v>
+        <v>618387</v>
       </c>
       <c r="R9" t="n">
-        <v>6974460</v>
+        <v>6974489</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1619,32 +1619,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129709813</v>
+        <v>129698674</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>91557</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618387</v>
+        <v>618306</v>
       </c>
       <c r="R10" t="n">
-        <v>6974489</v>
+        <v>6974462</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1823,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129709783</v>
+        <v>129709780</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>79113</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,21 +1834,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618335</v>
+        <v>618429</v>
       </c>
       <c r="R12" t="n">
-        <v>6974445</v>
+        <v>6974460</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1894,11 +1894,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,32 +1920,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129703570</v>
+        <v>129709783</v>
       </c>
       <c r="B13" t="n">
-        <v>80141</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1960,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618374</v>
+        <v>618335</v>
       </c>
       <c r="R13" t="n">
-        <v>6974569</v>
+        <v>6974445</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,6 +1991,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129698674</v>
+        <v>129703570</v>
       </c>
       <c r="B14" t="n">
-        <v>91552</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,21 +2033,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618306</v>
+        <v>618374</v>
       </c>
       <c r="R14" t="n">
-        <v>6974462</v>
+        <v>6974569</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129698604</v>
+        <v>129709792</v>
       </c>
       <c r="B15" t="n">
-        <v>80085</v>
+        <v>80214</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,21 +2130,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618306</v>
+        <v>618361</v>
       </c>
       <c r="R15" t="n">
-        <v>6974462</v>
+        <v>6974581</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,10 +2216,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129709792</v>
+        <v>129698604</v>
       </c>
       <c r="B16" t="n">
-        <v>80209</v>
+        <v>80090</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,21 +2227,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618361</v>
+        <v>618306</v>
       </c>
       <c r="R16" t="n">
-        <v>6974581</v>
+        <v>6974462</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129709808</v>
+        <v>129699517</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>91593</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,21 +2426,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>618368</v>
+        <v>618397</v>
       </c>
       <c r="R18" t="n">
-        <v>6974577</v>
+        <v>6974439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2515,7 +2515,7 @@
         <v>129699006</v>
       </c>
       <c r="B19" t="n">
-        <v>80209</v>
+        <v>80214</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>129703715</v>
       </c>
       <c r="B20" t="n">
-        <v>91602</v>
+        <v>91607</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129699517</v>
+        <v>129709808</v>
       </c>
       <c r="B21" t="n">
-        <v>91588</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>618397</v>
+        <v>618368</v>
       </c>
       <c r="R21" t="n">
-        <v>6974439</v>
+        <v>6974577</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
         <v>129709801</v>
       </c>
       <c r="B22" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>129700331</v>
       </c>
       <c r="B23" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>129709806</v>
       </c>
       <c r="B24" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129700673</v>
+        <v>129705121</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,39 +3114,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>618551</v>
+        <v>618113</v>
       </c>
       <c r="R25" t="n">
-        <v>6974411</v>
+        <v>6974574</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,11 +3174,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Sav/kåda syns från ett antal rader högt upp</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3317,10 +3307,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129705121</v>
+        <v>129700673</v>
       </c>
       <c r="B27" t="n">
-        <v>91588</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3328,34 +3318,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>618113</v>
+        <v>618551</v>
       </c>
       <c r="R27" t="n">
-        <v>6974574</v>
+        <v>6974411</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,6 +3383,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Sav/kåda syns från ett antal rader högt upp</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3417,7 +3417,7 @@
         <v>129704326</v>
       </c>
       <c r="B28" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,45 +3511,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129703585</v>
+        <v>129699831</v>
       </c>
       <c r="B29" t="n">
-        <v>80210</v>
+        <v>98774</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>618374</v>
+        <v>618439</v>
       </c>
       <c r="R29" t="n">
-        <v>6974569</v>
+        <v>6974411</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3608,10 +3612,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129705214</v>
+        <v>129705042</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>91891</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3619,39 +3623,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>618074</v>
+        <v>618126</v>
       </c>
       <c r="R30" t="n">
-        <v>6974557</v>
+        <v>6974589</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3684,11 +3683,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3715,49 +3709,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129699831</v>
+        <v>129703585</v>
       </c>
       <c r="B31" t="n">
-        <v>98769</v>
+        <v>80215</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>618439</v>
+        <v>618374</v>
       </c>
       <c r="R31" t="n">
-        <v>6974411</v>
+        <v>6974569</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3816,10 +3806,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129705042</v>
+        <v>129705214</v>
       </c>
       <c r="B32" t="n">
-        <v>91886</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3827,34 +3817,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>618126</v>
+        <v>618074</v>
       </c>
       <c r="R32" t="n">
-        <v>6974589</v>
+        <v>6974557</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3887,6 +3882,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3916,7 +3916,7 @@
         <v>129709797</v>
       </c>
       <c r="B33" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>129698910</v>
       </c>
       <c r="B34" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4121,32 +4121,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129709803</v>
+        <v>129709788</v>
       </c>
       <c r="B35" t="n">
-        <v>98769</v>
+        <v>91614</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>618554</v>
+        <v>618455</v>
       </c>
       <c r="R35" t="n">
-        <v>6974421</v>
+        <v>6974515</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4192,11 +4192,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>14 exemplar ca</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4223,45 +4218,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129704306</v>
+        <v>129704389</v>
       </c>
       <c r="B36" t="n">
-        <v>78834</v>
+        <v>98774</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>618272</v>
+        <v>618258</v>
       </c>
       <c r="R36" t="n">
-        <v>6974601</v>
+        <v>6974606</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4320,10 +4319,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129704389</v>
+        <v>129709803</v>
       </c>
       <c r="B37" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4348,21 +4347,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>618258</v>
+        <v>618554</v>
       </c>
       <c r="R37" t="n">
-        <v>6974606</v>
+        <v>6974421</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4395,6 +4390,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>14 exemplar ca</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4421,10 +4421,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129709788</v>
+        <v>129704306</v>
       </c>
       <c r="B38" t="n">
-        <v>91609</v>
+        <v>78839</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4432,21 +4432,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>618455</v>
+        <v>618272</v>
       </c>
       <c r="R38" t="n">
-        <v>6974515</v>
+        <v>6974601</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4518,10 +4518,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129701823</v>
+        <v>129700579</v>
       </c>
       <c r="B39" t="n">
-        <v>91588</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4529,34 +4529,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>618649</v>
+        <v>618530</v>
       </c>
       <c r="R39" t="n">
-        <v>6974391</v>
+        <v>6974383</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4589,6 +4594,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4615,7 +4625,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129700579</v>
+        <v>129700722</v>
       </c>
       <c r="B40" t="n">
         <v>57736</v>
@@ -4655,10 +4665,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>618530</v>
+        <v>618567</v>
       </c>
       <c r="R40" t="n">
-        <v>6974383</v>
+        <v>6974393</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4722,50 +4732,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129700722</v>
+        <v>129701961</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>80146</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>618567</v>
+        <v>618622</v>
       </c>
       <c r="R41" t="n">
-        <v>6974393</v>
+        <v>6974425</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4798,11 +4803,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4829,32 +4829,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129701961</v>
+        <v>129701823</v>
       </c>
       <c r="B42" t="n">
-        <v>80141</v>
+        <v>91593</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>618622</v>
+        <v>618649</v>
       </c>
       <c r="R42" t="n">
-        <v>6974425</v>
+        <v>6974391</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4929,7 +4929,7 @@
         <v>129704245</v>
       </c>
       <c r="B43" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>129701808</v>
       </c>
       <c r="B44" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5124,10 +5124,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129700093</v>
+        <v>129700433</v>
       </c>
       <c r="B45" t="n">
-        <v>80181</v>
+        <v>78838</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5135,21 +5135,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>618480</v>
+        <v>618512</v>
       </c>
       <c r="R45" t="n">
-        <v>6974430</v>
+        <v>6974407</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5221,45 +5221,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129700433</v>
+        <v>129700894</v>
       </c>
       <c r="B46" t="n">
-        <v>78833</v>
+        <v>98774</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>618512</v>
+        <v>618592</v>
       </c>
       <c r="R46" t="n">
-        <v>6974407</v>
+        <v>6974393</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5318,10 +5322,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129709804</v>
+        <v>129709802</v>
       </c>
       <c r="B47" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5353,10 +5357,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>618371</v>
+        <v>618567</v>
       </c>
       <c r="R47" t="n">
-        <v>6974493</v>
+        <v>6974470</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5393,7 +5397,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>100 stycken ca</t>
+          <t>100stycken ca</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5420,32 +5424,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129702152</v>
+        <v>129709804</v>
       </c>
       <c r="B48" t="n">
-        <v>91588</v>
+        <v>98774</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5455,10 +5459,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>618609</v>
+        <v>618371</v>
       </c>
       <c r="R48" t="n">
-        <v>6974445</v>
+        <v>6974493</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5491,6 +5495,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>100 stycken ca</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5517,10 +5526,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129701912</v>
+        <v>129702152</v>
       </c>
       <c r="B49" t="n">
-        <v>57733</v>
+        <v>91593</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5528,39 +5537,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>618633</v>
+        <v>618609</v>
       </c>
       <c r="R49" t="n">
-        <v>6974410</v>
+        <v>6974445</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5619,49 +5623,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129700894</v>
+        <v>129700093</v>
       </c>
       <c r="B50" t="n">
-        <v>98769</v>
+        <v>80186</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>618592</v>
+        <v>618480</v>
       </c>
       <c r="R50" t="n">
-        <v>6974393</v>
+        <v>6974430</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5720,45 +5720,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129709802</v>
+        <v>129701912</v>
       </c>
       <c r="B51" t="n">
-        <v>98769</v>
+        <v>57733</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>618567</v>
+        <v>618633</v>
       </c>
       <c r="R51" t="n">
-        <v>6974470</v>
+        <v>6974410</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5791,11 +5796,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>100stycken ca</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5822,10 +5822,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129704213</v>
+        <v>129698501</v>
       </c>
       <c r="B52" t="n">
-        <v>78833</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5833,34 +5833,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>618281</v>
+        <v>618299</v>
       </c>
       <c r="R52" t="n">
-        <v>6974552</v>
+        <v>6974415</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5893,6 +5898,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5919,10 +5929,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129700660</v>
+        <v>129704213</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5930,39 +5940,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>618570</v>
+        <v>618281</v>
       </c>
       <c r="R53" t="n">
-        <v>6974419</v>
+        <v>6974552</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5995,11 +6000,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6026,45 +6026,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129709795</v>
+        <v>129700660</v>
       </c>
       <c r="B54" t="n">
-        <v>98769</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>618177</v>
+        <v>618570</v>
       </c>
       <c r="R54" t="n">
-        <v>6974631</v>
+        <v>6974419</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6101,7 +6106,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>33 stycken ca</t>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6128,32 +6133,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129709790</v>
+        <v>129709795</v>
       </c>
       <c r="B55" t="n">
-        <v>97640</v>
+        <v>98774</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6163,10 +6168,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>618431</v>
+        <v>618177</v>
       </c>
       <c r="R55" t="n">
-        <v>6974524</v>
+        <v>6974631</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6199,6 +6204,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>33 stycken ca</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6225,50 +6235,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129698501</v>
+        <v>129709790</v>
       </c>
       <c r="B56" t="n">
-        <v>57736</v>
+        <v>97645</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>618299</v>
+        <v>618431</v>
       </c>
       <c r="R56" t="n">
-        <v>6974415</v>
+        <v>6974524</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6301,11 +6306,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6332,45 +6332,49 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129703746</v>
+        <v>129701964</v>
       </c>
       <c r="B57" t="n">
-        <v>91588</v>
+        <v>98774</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>618374</v>
+        <v>618599</v>
       </c>
       <c r="R57" t="n">
-        <v>6974569</v>
+        <v>6974439</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6429,50 +6433,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129702559</v>
+        <v>129709791</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>97645</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>618561</v>
+        <v>618571</v>
       </c>
       <c r="R58" t="n">
-        <v>6974470</v>
+        <v>6974415</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6505,11 +6504,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6536,38 +6530,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129701951</v>
+        <v>129698818</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>55</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6576,10 +6569,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>618605</v>
+        <v>618341</v>
       </c>
       <c r="R59" t="n">
-        <v>6974424</v>
+        <v>6974479</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6612,11 +6605,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhck av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6643,10 +6631,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129709786</v>
+        <v>129703746</v>
       </c>
       <c r="B60" t="n">
-        <v>57896</v>
+        <v>91593</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6654,21 +6642,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6678,10 +6666,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>618556</v>
+        <v>618374</v>
       </c>
       <c r="R60" t="n">
-        <v>6974460</v>
+        <v>6974569</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6714,11 +6702,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>2 stycken, födosöker. Övriga läten</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6745,37 +6728,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129701964</v>
+        <v>129702559</v>
       </c>
       <c r="B61" t="n">
-        <v>98769</v>
+        <v>57736</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6784,10 +6768,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>618599</v>
+        <v>618561</v>
       </c>
       <c r="R61" t="n">
-        <v>6974439</v>
+        <v>6974470</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6820,6 +6804,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6846,45 +6835,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129709791</v>
+        <v>129701951</v>
       </c>
       <c r="B62" t="n">
-        <v>97640</v>
+        <v>57736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>618571</v>
+        <v>618605</v>
       </c>
       <c r="R62" t="n">
-        <v>6974415</v>
+        <v>6974424</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6917,6 +6911,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhck av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6943,49 +6942,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129698818</v>
+        <v>129709786</v>
       </c>
       <c r="B63" t="n">
-        <v>98769</v>
+        <v>57896</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>618341</v>
+        <v>618556</v>
       </c>
       <c r="R63" t="n">
-        <v>6974479</v>
+        <v>6974460</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7018,6 +7013,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>2 stycken, födosöker. Övriga läten</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7044,45 +7044,49 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129704771</v>
+        <v>129700395</v>
       </c>
       <c r="B64" t="n">
-        <v>91602</v>
+        <v>98774</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>618289</v>
+        <v>618472</v>
       </c>
       <c r="R64" t="n">
-        <v>6974621</v>
+        <v>6974404</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7119,7 +7123,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Kan finnas mer under löven</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7146,32 +7150,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129709810</v>
+        <v>129709799</v>
       </c>
       <c r="B65" t="n">
-        <v>79076</v>
+        <v>98774</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7181,10 +7185,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>618631</v>
+        <v>618358</v>
       </c>
       <c r="R65" t="n">
-        <v>6974375</v>
+        <v>6974576</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7217,6 +7221,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>100 stycken ca</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7243,10 +7252,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129709809</v>
+        <v>129704771</v>
       </c>
       <c r="B66" t="n">
-        <v>79076</v>
+        <v>91607</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7254,21 +7263,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7278,10 +7287,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>618431</v>
+        <v>618289</v>
       </c>
       <c r="R66" t="n">
-        <v>6974524</v>
+        <v>6974621</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7314,6 +7323,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7340,10 +7354,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129709787</v>
+        <v>129709810</v>
       </c>
       <c r="B67" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7351,21 +7365,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7375,10 +7389,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>618429</v>
+        <v>618631</v>
       </c>
       <c r="R67" t="n">
-        <v>6974460</v>
+        <v>6974375</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7411,11 +7425,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Övriga läten</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7442,49 +7451,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129700395</v>
+        <v>129709809</v>
       </c>
       <c r="B68" t="n">
-        <v>98769</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>618472</v>
+        <v>618431</v>
       </c>
       <c r="R68" t="n">
-        <v>6974404</v>
+        <v>6974524</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7517,11 +7522,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Kan finnas mer under löven</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7548,32 +7548,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129709799</v>
+        <v>129709787</v>
       </c>
       <c r="B69" t="n">
-        <v>98769</v>
+        <v>57896</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7583,10 +7583,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>618358</v>
+        <v>618429</v>
       </c>
       <c r="R69" t="n">
-        <v>6974576</v>
+        <v>6974460</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>100 stycken ca</t>
+          <t>Övriga läten</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7650,32 +7650,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129701187</v>
+        <v>129699772</v>
       </c>
       <c r="B70" t="n">
-        <v>91588</v>
+        <v>97645</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7685,10 +7685,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>618641</v>
+        <v>618405</v>
       </c>
       <c r="R70" t="n">
-        <v>6974337</v>
+        <v>6974427</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7747,10 +7747,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129709782</v>
+        <v>129701187</v>
       </c>
       <c r="B71" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7758,21 +7758,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7782,10 +7782,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>618425</v>
+        <v>618641</v>
       </c>
       <c r="R71" t="n">
-        <v>6974448</v>
+        <v>6974337</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7818,11 +7818,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7849,32 +7844,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129699772</v>
+        <v>129709782</v>
       </c>
       <c r="B72" t="n">
-        <v>97640</v>
+        <v>57736</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7884,10 +7879,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>618405</v>
+        <v>618425</v>
       </c>
       <c r="R72" t="n">
-        <v>6974427</v>
+        <v>6974448</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7920,6 +7915,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7946,45 +7946,49 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129709794</v>
+        <v>129702470</v>
       </c>
       <c r="B73" t="n">
-        <v>80181</v>
+        <v>98774</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>618395</v>
+        <v>618556</v>
       </c>
       <c r="R73" t="n">
-        <v>6974510</v>
+        <v>6974479</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8043,32 +8047,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129701841</v>
+        <v>129709800</v>
       </c>
       <c r="B74" t="n">
-        <v>91886</v>
+        <v>98774</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8078,10 +8082,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>618649</v>
+        <v>618497</v>
       </c>
       <c r="R74" t="n">
-        <v>6974391</v>
+        <v>6974486</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8114,6 +8118,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>11 stycken ca</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8140,32 +8149,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129704757</v>
+        <v>129709794</v>
       </c>
       <c r="B75" t="n">
-        <v>91761</v>
+        <v>80186</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8175,10 +8184,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>618292</v>
+        <v>618395</v>
       </c>
       <c r="R75" t="n">
-        <v>6974613</v>
+        <v>6974510</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8237,49 +8246,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129702470</v>
+        <v>129701841</v>
       </c>
       <c r="B76" t="n">
-        <v>98769</v>
+        <v>91891</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>618556</v>
+        <v>618649</v>
       </c>
       <c r="R76" t="n">
-        <v>6974479</v>
+        <v>6974391</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8338,10 +8343,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129709800</v>
+        <v>129704757</v>
       </c>
       <c r="B77" t="n">
-        <v>98769</v>
+        <v>91766</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8349,21 +8354,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8373,10 +8378,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>618497</v>
+        <v>618292</v>
       </c>
       <c r="R77" t="n">
-        <v>6974486</v>
+        <v>6974613</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8409,11 +8414,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>11 stycken ca</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8440,10 +8440,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129709807</v>
+        <v>129699521</v>
       </c>
       <c r="B78" t="n">
-        <v>91608</v>
+        <v>91891</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8451,19 +8451,23 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8471,10 +8475,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>618463</v>
+        <v>618397</v>
       </c>
       <c r="R78" t="n">
-        <v>6974461</v>
+        <v>6974439</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8533,10 +8537,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129700014</v>
+        <v>129709807</v>
       </c>
       <c r="B79" t="n">
-        <v>57736</v>
+        <v>91613</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8544,39 +8548,30 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>618472</v>
+        <v>618463</v>
       </c>
       <c r="R79" t="n">
-        <v>6974404</v>
+        <v>6974461</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8609,11 +8604,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8640,32 +8630,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129699521</v>
+        <v>129709798</v>
       </c>
       <c r="B80" t="n">
-        <v>91886</v>
+        <v>98774</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8675,10 +8665,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>618397</v>
+        <v>618348</v>
       </c>
       <c r="R80" t="n">
-        <v>6974439</v>
+        <v>6974608</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8711,6 +8701,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>36 stycken ca</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8737,32 +8732,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129709798</v>
+        <v>129702960</v>
       </c>
       <c r="B81" t="n">
-        <v>98769</v>
+        <v>78838</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8772,10 +8767,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>618348</v>
+        <v>618489</v>
       </c>
       <c r="R81" t="n">
-        <v>6974608</v>
+        <v>6974558</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8808,11 +8803,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>36 stycken ca</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8839,10 +8829,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129702960</v>
+        <v>129700014</v>
       </c>
       <c r="B82" t="n">
-        <v>78833</v>
+        <v>57736</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8850,34 +8840,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>618489</v>
+        <v>618472</v>
       </c>
       <c r="R82" t="n">
-        <v>6974558</v>
+        <v>6974404</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8910,6 +8905,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9153,7 +9153,7 @@
         <v>129703426</v>
       </c>
       <c r="B85" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>129709805</v>
       </c>
       <c r="B86" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>129704982</v>
       </c>
       <c r="B87" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9446,10 +9446,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129702218</v>
+        <v>129700937</v>
       </c>
       <c r="B88" t="n">
-        <v>91588</v>
+        <v>90625</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9457,21 +9457,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>1962</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9481,10 +9481,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>618623</v>
+        <v>618593</v>
       </c>
       <c r="R88" t="n">
-        <v>6974450</v>
+        <v>6974355</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9543,10 +9543,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129700937</v>
+        <v>129702218</v>
       </c>
       <c r="B89" t="n">
-        <v>90620</v>
+        <v>91593</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9554,21 +9554,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1962</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9578,10 +9578,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>618593</v>
+        <v>618623</v>
       </c>
       <c r="R89" t="n">
-        <v>6974355</v>
+        <v>6974450</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9643,7 +9643,7 @@
         <v>129703590</v>
       </c>
       <c r="B90" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>129709796</v>
       </c>
       <c r="B91" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9839,32 +9839,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129698786</v>
+        <v>129709793</v>
       </c>
       <c r="B92" t="n">
-        <v>79076</v>
+        <v>80214</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9874,10 +9874,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>618352</v>
+        <v>618444</v>
       </c>
       <c r="R92" t="n">
-        <v>6974455</v>
+        <v>6974454</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9936,10 +9936,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129700358</v>
+        <v>129703072</v>
       </c>
       <c r="B93" t="n">
-        <v>97640</v>
+        <v>80214</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9947,21 +9947,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9971,10 +9971,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>618459</v>
+        <v>618475</v>
       </c>
       <c r="R93" t="n">
-        <v>6974445</v>
+        <v>6974567</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10033,10 +10033,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129709793</v>
+        <v>129700358</v>
       </c>
       <c r="B94" t="n">
-        <v>80209</v>
+        <v>97645</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10044,21 +10044,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10068,10 +10068,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>618444</v>
+        <v>618459</v>
       </c>
       <c r="R94" t="n">
-        <v>6974454</v>
+        <v>6974445</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10130,32 +10130,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129703072</v>
+        <v>129698786</v>
       </c>
       <c r="B95" t="n">
-        <v>80209</v>
+        <v>79081</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10165,10 +10165,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>618475</v>
+        <v>618352</v>
       </c>
       <c r="R95" t="n">
-        <v>6974567</v>
+        <v>6974455</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10230,7 +10230,7 @@
         <v>129699107</v>
       </c>
       <c r="B96" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10328,10 +10328,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129705055</v>
+        <v>129699630</v>
       </c>
       <c r="B97" t="n">
-        <v>91588</v>
+        <v>78839</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10339,21 +10339,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10363,10 +10363,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>618126</v>
+        <v>618397</v>
       </c>
       <c r="R97" t="n">
-        <v>6974604</v>
+        <v>6974439</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10425,32 +10425,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129701836</v>
+        <v>129705055</v>
       </c>
       <c r="B98" t="n">
-        <v>92041</v>
+        <v>91593</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>618649</v>
+        <v>618126</v>
       </c>
       <c r="R98" t="n">
-        <v>6974391</v>
+        <v>6974604</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10522,32 +10522,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129703875</v>
+        <v>129701836</v>
       </c>
       <c r="B99" t="n">
-        <v>88987</v>
+        <v>92046</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>510</v>
+        <v>1209</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10557,10 +10557,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>618370</v>
+        <v>618649</v>
       </c>
       <c r="R99" t="n">
-        <v>6974548</v>
+        <v>6974391</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10619,10 +10619,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129700040</v>
+        <v>129703875</v>
       </c>
       <c r="B100" t="n">
-        <v>57736</v>
+        <v>88992</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10630,39 +10630,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>618488</v>
+        <v>618370</v>
       </c>
       <c r="R100" t="n">
-        <v>6974408</v>
+        <v>6974548</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10695,11 +10690,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Många äldre ringhack, men en färsk rad</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10726,7 +10716,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129700503</v>
+        <v>129700040</v>
       </c>
       <c r="B101" t="n">
         <v>57736</v>
@@ -10757,7 +10747,7 @@
       <c r="I101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -10766,10 +10756,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>618531</v>
+        <v>618488</v>
       </c>
       <c r="R101" t="n">
-        <v>6974409</v>
+        <v>6974408</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10806,7 +10796,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall. Många äldre ringhack, men en färsk rad</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10833,10 +10823,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129699630</v>
+        <v>129700503</v>
       </c>
       <c r="B102" t="n">
-        <v>78834</v>
+        <v>57736</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10844,34 +10834,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>618397</v>
+        <v>618531</v>
       </c>
       <c r="R102" t="n">
-        <v>6974439</v>
+        <v>6974409</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10904,6 +10899,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11047,7 +11047,7 @@
         <v>129701109</v>
       </c>
       <c r="B104" t="n">
-        <v>91761</v>
+        <v>91766</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 53262-2025 artfynd.xlsx
+++ b/artfynd/A 53262-2025 artfynd.xlsx
@@ -1619,32 +1619,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129698674</v>
+        <v>129709783</v>
       </c>
       <c r="B10" t="n">
-        <v>91557</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618306</v>
+        <v>618335</v>
       </c>
       <c r="R10" t="n">
-        <v>6974462</v>
+        <v>6974445</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,6 +1690,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,50 +1721,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129698621</v>
+        <v>129703570</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>80146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618317</v>
+        <v>618374</v>
       </c>
       <c r="R11" t="n">
-        <v>6974462</v>
+        <v>6974569</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,11 +1792,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1920,32 +1915,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129709783</v>
+        <v>129698674</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>91557</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1955,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618335</v>
+        <v>618306</v>
       </c>
       <c r="R13" t="n">
-        <v>6974445</v>
+        <v>6974462</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1991,11 +1986,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,45 +2012,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129703570</v>
+        <v>129698621</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618374</v>
+        <v>618317</v>
       </c>
       <c r="R14" t="n">
-        <v>6974569</v>
+        <v>6974462</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2093,6 +2088,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129709792</v>
+        <v>129698604</v>
       </c>
       <c r="B15" t="n">
-        <v>80214</v>
+        <v>80090</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,21 +2130,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618361</v>
+        <v>618306</v>
       </c>
       <c r="R15" t="n">
-        <v>6974581</v>
+        <v>6974462</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,32 +2216,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129698604</v>
+        <v>129709781</v>
       </c>
       <c r="B16" t="n">
-        <v>80090</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618306</v>
+        <v>618592</v>
       </c>
       <c r="R16" t="n">
-        <v>6974462</v>
+        <v>6974467</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2287,6 +2287,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,32 +2318,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129709781</v>
+        <v>129709792</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>80214</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2348,10 +2353,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618592</v>
+        <v>618361</v>
       </c>
       <c r="R17" t="n">
-        <v>6974467</v>
+        <v>6974581</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2384,11 +2389,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2415,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129699517</v>
+        <v>129709808</v>
       </c>
       <c r="B18" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,21 +2426,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>618397</v>
+        <v>618368</v>
       </c>
       <c r="R18" t="n">
-        <v>6974439</v>
+        <v>6974577</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129703715</v>
+        <v>129699517</v>
       </c>
       <c r="B20" t="n">
-        <v>91607</v>
+        <v>91593</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2620,21 +2620,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>618370</v>
+        <v>618397</v>
       </c>
       <c r="R20" t="n">
-        <v>6974548</v>
+        <v>6974439</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129709808</v>
+        <v>129703715</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>91607</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>618368</v>
+        <v>618370</v>
       </c>
       <c r="R21" t="n">
-        <v>6974577</v>
+        <v>6974548</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129705121</v>
+        <v>129700673</v>
       </c>
       <c r="B25" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,34 +3114,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>618113</v>
+        <v>618551</v>
       </c>
       <c r="R25" t="n">
-        <v>6974574</v>
+        <v>6974411</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3174,6 +3179,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Sav/kåda syns från ett antal rader högt upp</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3200,10 +3210,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129699154</v>
+        <v>129705121</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3211,39 +3221,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>618371</v>
+        <v>618113</v>
       </c>
       <c r="R26" t="n">
-        <v>6974482</v>
+        <v>6974574</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3276,11 +3281,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3307,7 +3307,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129700673</v>
+        <v>129699154</v>
       </c>
       <c r="B27" t="n">
         <v>57736</v>
@@ -3338,7 +3338,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>618551</v>
+        <v>618371</v>
       </c>
       <c r="R27" t="n">
-        <v>6974411</v>
+        <v>6974482</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Sav/kåda syns från ett antal rader högt upp</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3511,49 +3511,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129699831</v>
+        <v>129703585</v>
       </c>
       <c r="B29" t="n">
-        <v>98774</v>
+        <v>80215</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>618439</v>
+        <v>618374</v>
       </c>
       <c r="R29" t="n">
-        <v>6974411</v>
+        <v>6974569</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3612,10 +3608,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129705042</v>
+        <v>129705214</v>
       </c>
       <c r="B30" t="n">
-        <v>91891</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3623,34 +3619,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>618126</v>
+        <v>618074</v>
       </c>
       <c r="R30" t="n">
-        <v>6974589</v>
+        <v>6974557</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3683,6 +3684,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3709,45 +3715,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129703585</v>
+        <v>129699831</v>
       </c>
       <c r="B31" t="n">
-        <v>80215</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>618374</v>
+        <v>618439</v>
       </c>
       <c r="R31" t="n">
-        <v>6974569</v>
+        <v>6974411</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3806,10 +3816,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129705214</v>
+        <v>129705042</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>91891</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3817,39 +3827,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>618074</v>
+        <v>618126</v>
       </c>
       <c r="R32" t="n">
-        <v>6974557</v>
+        <v>6974589</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3882,11 +3887,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4218,49 +4218,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129704389</v>
+        <v>129704306</v>
       </c>
       <c r="B36" t="n">
-        <v>98774</v>
+        <v>78839</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>618258</v>
+        <v>618272</v>
       </c>
       <c r="R36" t="n">
-        <v>6974606</v>
+        <v>6974601</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4319,7 +4315,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129709803</v>
+        <v>129704389</v>
       </c>
       <c r="B37" t="n">
         <v>98774</v>
@@ -4347,17 +4343,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>618554</v>
+        <v>618258</v>
       </c>
       <c r="R37" t="n">
-        <v>6974421</v>
+        <v>6974606</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4390,11 +4390,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>14 exemplar ca</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4421,32 +4416,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129704306</v>
+        <v>129709803</v>
       </c>
       <c r="B38" t="n">
-        <v>78839</v>
+        <v>98774</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4456,10 +4451,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>618272</v>
+        <v>618554</v>
       </c>
       <c r="R38" t="n">
-        <v>6974601</v>
+        <v>6974421</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4492,6 +4487,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>14 exemplar ca</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4518,10 +4518,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129700579</v>
+        <v>129701823</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4529,39 +4529,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>618530</v>
+        <v>618649</v>
       </c>
       <c r="R39" t="n">
-        <v>6974383</v>
+        <v>6974391</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4594,11 +4589,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4625,50 +4615,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129700722</v>
+        <v>129701961</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>80146</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>618567</v>
+        <v>618622</v>
       </c>
       <c r="R40" t="n">
-        <v>6974393</v>
+        <v>6974425</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4701,11 +4686,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4732,32 +4712,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129701961</v>
+        <v>129701808</v>
       </c>
       <c r="B41" t="n">
-        <v>80146</v>
+        <v>80186</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4767,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>618622</v>
+        <v>618645</v>
       </c>
       <c r="R41" t="n">
-        <v>6974425</v>
+        <v>6974380</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4829,10 +4809,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129701823</v>
+        <v>129700579</v>
       </c>
       <c r="B42" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4840,34 +4820,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>618649</v>
+        <v>618530</v>
       </c>
       <c r="R42" t="n">
-        <v>6974391</v>
+        <v>6974383</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4900,6 +4885,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4926,37 +4916,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129704245</v>
+        <v>129700722</v>
       </c>
       <c r="B43" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4965,10 +4956,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>618265</v>
+        <v>618567</v>
       </c>
       <c r="R43" t="n">
-        <v>6974571</v>
+        <v>6974393</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5001,6 +4992,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5027,45 +5023,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129701808</v>
+        <v>129704245</v>
       </c>
       <c r="B44" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>618645</v>
+        <v>618265</v>
       </c>
       <c r="R44" t="n">
-        <v>6974380</v>
+        <v>6974571</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5929,10 +5929,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129704213</v>
+        <v>129700660</v>
       </c>
       <c r="B53" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5940,34 +5940,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>618281</v>
+        <v>618570</v>
       </c>
       <c r="R53" t="n">
-        <v>6974552</v>
+        <v>6974419</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6000,6 +6005,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6026,10 +6036,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129700660</v>
+        <v>129704213</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6037,39 +6047,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>618570</v>
+        <v>618281</v>
       </c>
       <c r="R54" t="n">
-        <v>6974419</v>
+        <v>6974552</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6102,11 +6107,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6332,7 +6332,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129701964</v>
+        <v>129698818</v>
       </c>
       <c r="B57" t="n">
         <v>98774</v>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>55</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>618599</v>
+        <v>618341</v>
       </c>
       <c r="R57" t="n">
-        <v>6974439</v>
+        <v>6974479</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6433,32 +6433,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129709791</v>
+        <v>129703746</v>
       </c>
       <c r="B58" t="n">
-        <v>97645</v>
+        <v>91593</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>618571</v>
+        <v>618374</v>
       </c>
       <c r="R58" t="n">
-        <v>6974415</v>
+        <v>6974569</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6530,49 +6530,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129698818</v>
+        <v>129709786</v>
       </c>
       <c r="B59" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>618341</v>
+        <v>618556</v>
       </c>
       <c r="R59" t="n">
-        <v>6974479</v>
+        <v>6974460</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6605,6 +6601,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>2 stycken, födosöker. Övriga läten</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6631,45 +6632,49 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129703746</v>
+        <v>129701964</v>
       </c>
       <c r="B60" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>618374</v>
+        <v>618599</v>
       </c>
       <c r="R60" t="n">
-        <v>6974569</v>
+        <v>6974439</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6728,50 +6733,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129702559</v>
+        <v>129709791</v>
       </c>
       <c r="B61" t="n">
-        <v>57736</v>
+        <v>97645</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>618561</v>
+        <v>618571</v>
       </c>
       <c r="R61" t="n">
-        <v>6974470</v>
+        <v>6974415</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6804,11 +6804,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6835,7 +6830,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129701951</v>
+        <v>129702559</v>
       </c>
       <c r="B62" t="n">
         <v>57736</v>
@@ -6866,7 +6861,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6875,10 +6870,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>618605</v>
+        <v>618561</v>
       </c>
       <c r="R62" t="n">
-        <v>6974424</v>
+        <v>6974470</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6915,7 +6910,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhck av tretåig hackspett på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6942,10 +6937,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129709786</v>
+        <v>129701951</v>
       </c>
       <c r="B63" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6953,34 +6948,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>618556</v>
+        <v>618605</v>
       </c>
       <c r="R63" t="n">
-        <v>6974460</v>
+        <v>6974424</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>2 stycken, födosöker. Övriga läten</t>
+          <t>Ringhck av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7044,49 +7044,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129700395</v>
+        <v>129709787</v>
       </c>
       <c r="B64" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>618472</v>
+        <v>618429</v>
       </c>
       <c r="R64" t="n">
-        <v>6974404</v>
+        <v>6974460</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7123,7 +7119,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Kan finnas mer under löven</t>
+          <t>Övriga läten</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7150,32 +7146,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129709799</v>
+        <v>129704771</v>
       </c>
       <c r="B65" t="n">
-        <v>98774</v>
+        <v>91607</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7185,10 +7181,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>618358</v>
+        <v>618289</v>
       </c>
       <c r="R65" t="n">
-        <v>6974576</v>
+        <v>6974621</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7225,7 +7221,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>100 stycken ca</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7252,10 +7248,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129704771</v>
+        <v>129709810</v>
       </c>
       <c r="B66" t="n">
-        <v>91607</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7263,21 +7259,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7287,10 +7283,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>618289</v>
+        <v>618631</v>
       </c>
       <c r="R66" t="n">
-        <v>6974621</v>
+        <v>6974375</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7323,11 +7319,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7354,7 +7345,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129709810</v>
+        <v>129709809</v>
       </c>
       <c r="B67" t="n">
         <v>79081</v>
@@ -7389,10 +7380,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>618631</v>
+        <v>618431</v>
       </c>
       <c r="R67" t="n">
-        <v>6974375</v>
+        <v>6974524</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7451,45 +7442,49 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129709809</v>
+        <v>129700395</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>618431</v>
+        <v>618472</v>
       </c>
       <c r="R68" t="n">
-        <v>6974524</v>
+        <v>6974404</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7522,6 +7517,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Kan finnas mer under löven</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7548,32 +7548,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129709787</v>
+        <v>129709799</v>
       </c>
       <c r="B69" t="n">
-        <v>57896</v>
+        <v>98774</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7583,10 +7583,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>618429</v>
+        <v>618358</v>
       </c>
       <c r="R69" t="n">
-        <v>6974460</v>
+        <v>6974576</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Övriga läten</t>
+          <t>100 stycken ca</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7946,49 +7946,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129702470</v>
+        <v>129701841</v>
       </c>
       <c r="B73" t="n">
-        <v>98774</v>
+        <v>91891</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>618556</v>
+        <v>618649</v>
       </c>
       <c r="R73" t="n">
-        <v>6974479</v>
+        <v>6974391</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8047,10 +8043,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129709800</v>
+        <v>129704757</v>
       </c>
       <c r="B74" t="n">
-        <v>98774</v>
+        <v>91766</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8058,21 +8054,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8082,10 +8078,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>618497</v>
+        <v>618292</v>
       </c>
       <c r="R74" t="n">
-        <v>6974486</v>
+        <v>6974613</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8118,11 +8114,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>11 stycken ca</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8246,45 +8237,49 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129701841</v>
+        <v>129702470</v>
       </c>
       <c r="B76" t="n">
-        <v>91891</v>
+        <v>98774</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>618649</v>
+        <v>618556</v>
       </c>
       <c r="R76" t="n">
-        <v>6974391</v>
+        <v>6974479</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8343,10 +8338,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129704757</v>
+        <v>129709800</v>
       </c>
       <c r="B77" t="n">
-        <v>91766</v>
+        <v>98774</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8354,21 +8349,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8378,10 +8373,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>618292</v>
+        <v>618497</v>
       </c>
       <c r="R77" t="n">
-        <v>6974613</v>
+        <v>6974486</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8414,6 +8409,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>11 stycken ca</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8630,32 +8630,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129709798</v>
+        <v>129702960</v>
       </c>
       <c r="B80" t="n">
-        <v>98774</v>
+        <v>78838</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8665,10 +8665,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>618348</v>
+        <v>618489</v>
       </c>
       <c r="R80" t="n">
-        <v>6974608</v>
+        <v>6974558</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8701,11 +8701,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>36 stycken ca</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8732,10 +8727,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129702960</v>
+        <v>129700014</v>
       </c>
       <c r="B81" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8743,34 +8738,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>618489</v>
+        <v>618472</v>
       </c>
       <c r="R81" t="n">
-        <v>6974558</v>
+        <v>6974404</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8803,6 +8803,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8829,50 +8834,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129700014</v>
+        <v>129709798</v>
       </c>
       <c r="B82" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>618472</v>
+        <v>618348</v>
       </c>
       <c r="R82" t="n">
-        <v>6974404</v>
+        <v>6974608</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>36 stycken ca</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8936,10 +8936,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129699933</v>
+        <v>129703426</v>
       </c>
       <c r="B83" t="n">
-        <v>57736</v>
+        <v>91891</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8947,39 +8947,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>618429</v>
+        <v>618409</v>
       </c>
       <c r="R83" t="n">
-        <v>6974385</v>
+        <v>6974571</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9012,11 +9007,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9043,7 +9033,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129699496</v>
+        <v>129699933</v>
       </c>
       <c r="B84" t="n">
         <v>57736</v>
@@ -9074,7 +9064,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9083,10 +9073,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>618397</v>
+        <v>618429</v>
       </c>
       <c r="R84" t="n">
-        <v>6974439</v>
+        <v>6974385</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9150,10 +9140,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129703426</v>
+        <v>129699496</v>
       </c>
       <c r="B85" t="n">
-        <v>91891</v>
+        <v>57736</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9161,34 +9151,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>618409</v>
+        <v>618397</v>
       </c>
       <c r="R85" t="n">
-        <v>6974571</v>
+        <v>6974439</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9221,6 +9216,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9839,32 +9839,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129709793</v>
+        <v>129698786</v>
       </c>
       <c r="B92" t="n">
-        <v>80214</v>
+        <v>79081</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9874,10 +9874,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>618444</v>
+        <v>618352</v>
       </c>
       <c r="R92" t="n">
-        <v>6974454</v>
+        <v>6974455</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9936,10 +9936,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129703072</v>
+        <v>129700358</v>
       </c>
       <c r="B93" t="n">
-        <v>80214</v>
+        <v>97645</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9947,21 +9947,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9971,10 +9971,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>618475</v>
+        <v>618459</v>
       </c>
       <c r="R93" t="n">
-        <v>6974567</v>
+        <v>6974445</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10033,45 +10033,49 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129700358</v>
+        <v>129699107</v>
       </c>
       <c r="B94" t="n">
-        <v>97645</v>
+        <v>98774</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>618459</v>
+        <v>618371</v>
       </c>
       <c r="R94" t="n">
-        <v>6974445</v>
+        <v>6974482</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10130,32 +10134,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129698786</v>
+        <v>129709793</v>
       </c>
       <c r="B95" t="n">
-        <v>79081</v>
+        <v>80214</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10165,10 +10169,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>618352</v>
+        <v>618444</v>
       </c>
       <c r="R95" t="n">
-        <v>6974455</v>
+        <v>6974454</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10227,49 +10231,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129699107</v>
+        <v>129703072</v>
       </c>
       <c r="B96" t="n">
-        <v>98774</v>
+        <v>80214</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>618371</v>
+        <v>618475</v>
       </c>
       <c r="R96" t="n">
-        <v>6974482</v>
+        <v>6974567</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10328,10 +10328,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129699630</v>
+        <v>129703875</v>
       </c>
       <c r="B97" t="n">
-        <v>78839</v>
+        <v>88992</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10339,21 +10339,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>510</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10363,10 +10363,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>618397</v>
+        <v>618370</v>
       </c>
       <c r="R97" t="n">
-        <v>6974439</v>
+        <v>6974548</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129705055</v>
+        <v>129700040</v>
       </c>
       <c r="B98" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10436,34 +10436,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>618126</v>
+        <v>618488</v>
       </c>
       <c r="R98" t="n">
-        <v>6974604</v>
+        <v>6974408</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10496,6 +10501,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Många äldre ringhack, men en färsk rad</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10522,45 +10532,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129701836</v>
+        <v>129700503</v>
       </c>
       <c r="B99" t="n">
-        <v>92046</v>
+        <v>57736</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>618649</v>
+        <v>618531</v>
       </c>
       <c r="R99" t="n">
-        <v>6974391</v>
+        <v>6974409</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10593,6 +10608,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10619,10 +10639,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129703875</v>
+        <v>129699630</v>
       </c>
       <c r="B100" t="n">
-        <v>88992</v>
+        <v>78839</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10630,21 +10650,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>510</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10654,10 +10674,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>618370</v>
+        <v>618397</v>
       </c>
       <c r="R100" t="n">
-        <v>6974548</v>
+        <v>6974439</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10716,10 +10736,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129700040</v>
+        <v>129705055</v>
       </c>
       <c r="B101" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10727,39 +10747,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>618488</v>
+        <v>618126</v>
       </c>
       <c r="R101" t="n">
-        <v>6974408</v>
+        <v>6974604</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10792,11 +10807,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Många äldre ringhack, men en färsk rad</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10823,50 +10833,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129700503</v>
+        <v>129701836</v>
       </c>
       <c r="B102" t="n">
-        <v>57736</v>
+        <v>92046</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Asketjärnen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>618531</v>
+        <v>618649</v>
       </c>
       <c r="R102" t="n">
-        <v>6974409</v>
+        <v>6974391</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10899,11 +10904,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD102" t="b">
